--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_MEXICO_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NEW_MEXICO_2021.xlsx
@@ -2767,7 +2767,7 @@
         <v>43</v>
       </c>
       <c r="D134">
-        <v>0.009641255605381167</v>
+        <v>0.009641255605381168</v>
       </c>
     </row>
     <row r="135">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C200">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C206">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C405">
